--- a/social media/B2/Reading4.xlsx
+++ b/social media/B2/Reading4.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,313 +413,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI51"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>f2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>f4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>f5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>f6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>k1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>k4</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>k5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>k6</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>b5</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>b6</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>a2</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>a3</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>a4</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>a5</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>a6</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_1</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_2</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_3</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_4</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_5</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_6</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_1</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_2</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_3</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_4</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_5</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_6</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_1</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_2</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_3</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_4</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_5</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_6</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_1</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_2</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_3</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_4</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_5</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_6</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_1</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_2</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_3</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_4</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_5</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_6</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_1</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_2</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_3</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_4</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_5</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_6</t>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>s4</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>s5</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>s6</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>r1_1</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>r1_2</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>r1_3</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>r1_4</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>r1_5</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>r1_6</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>r2_1</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>r2_2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>r2_3</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>r2_4</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>r2_5</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>r2_6</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>r3_1</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>r3_2</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>r3_3</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>r3_4</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>r3_5</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>r3_6</t>
         </is>
       </c>
     </row>
@@ -795,122 +671,62 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>You don't</t>
+          <t>You don't (1) _________ early.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that I fell asleep.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>She has</t>
+          <t>She has (1) _________ playing the piano.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>This machine hasn't</t>
+          <t>This machine hasn't (1) _________ for months.</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>You'll succeed</t>
+          <t>You'll succeed (1) _________ you work hard.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>She has been working here</t>
+          <t>She has been working here (1) _________ years.</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>early.</t>
+          <t>have to arrive</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>that I fell asleep.</t>
+          <t>such a boring film</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>playing the piano.</t>
+          <t>given up</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>for months.</t>
+          <t>been repaired</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>you work hard.</t>
+          <t>as long as</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>years.</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>given</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>as long</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>to arrive</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>a boring film</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>repaired</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>ten</t>
+          <t>for ten</t>
         </is>
       </c>
     </row>
@@ -982,122 +798,62 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The teacher</t>
+          <t>The teacher (1) _________ to open our books.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>If I had a car, I</t>
+          <t>If I had a car, I (1) _________ to work.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>She isn't</t>
+          <t>She isn't (1) _________ to reach the top shelf.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>We</t>
+          <t>We (1) _________ our leaking pipe fixed.</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ the gym.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Do you</t>
+          <t>Do you (1) _________ is?</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>to open our books.</t>
+          <t>told us</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>to work.</t>
+          <t>would drive</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>to reach the top shelf.</t>
+          <t>tall enough</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>our leaking pipe fixed.</t>
+          <t>had a plumber fix</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>the gym.</t>
+          <t>used to go to</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>is?</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>told</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>would</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>know</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>drive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>a plumber fix</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>go to</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>where the nearest hospital</t>
+          <t>know where the nearest hospital</t>
         </is>
       </c>
     </row>
@@ -1169,122 +925,62 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>I have been learning Spanish</t>
+          <t>I have been learning Spanish (1) _________ years.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>My new phone is</t>
+          <t>My new phone is (1) _________ my old one.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>She finished the report</t>
+          <t>She finished the report (1) _________ tired.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>I'll help you</t>
+          <t>I'll help you (1) _________ you ask me nicely.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ harder at school.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ a walk every morning.</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>years.</t>
+          <t>for two</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>my old one.</t>
+          <t>worse than</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>tired.</t>
+          <t>despite being</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>you ask me nicely.</t>
+          <t>as long as</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>harder at school.</t>
+          <t>wish I had studied</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>a walk every morning.</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>worse</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>despite</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>as long</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>two</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>than</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>I had studied</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>take</t>
+          <t>used to take</t>
         </is>
       </c>
     </row>
@@ -1356,122 +1052,62 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>French (1) _________ in this part of Belgium.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that I couldn't sleep.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>The manager</t>
+          <t>The manager (1) _________ the meeting.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ was very hungry.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>The bedroom hasn't</t>
+          <t>The bedroom hasn't (1) _________ yet.</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>My father</t>
+          <t>My father (1) _________ me stories.</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>in this part of Belgium.</t>
+          <t>is spoken</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>that I couldn't sleep.</t>
+          <t>such strong coffee</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>the meeting.</t>
+          <t>called off</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>was very hungry.</t>
+          <t>said (that) he</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>yet.</t>
+          <t>been decorated</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>me stories.</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>called</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>said</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>spoken</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>strong coffee</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>off</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>(that) he</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>decorated</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>tell</t>
+          <t>used to tell</t>
         </is>
       </c>
     </row>
@@ -1543,122 +1179,62 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ repaired last week.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Maria is</t>
+          <t>Maria is (1) _________ in the class.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>I'll lend you my notes</t>
+          <t>I'll lend you my notes (1) _________ you need them.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ his parents more often.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the wrong train.</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Do you</t>
+          <t>Do you (1) _________ the last bus leaves?</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>repaired last week.</t>
+          <t>got my car</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>in the class.</t>
+          <t>the fastest student</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>you need them.</t>
+          <t>provided that</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>his parents more often.</t>
+          <t>wishes he had called</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>the wrong train.</t>
+          <t>might have taken</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>the last bus leaves?</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>got</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>the fastest</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>provided</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>wishes</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>know</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>my car</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>student</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>that</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>he had called</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>have taken</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>what time</t>
+          <t>know what time</t>
         </is>
       </c>
     </row>
@@ -1730,122 +1306,62 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ about the appointment.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that we left early.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ a new business last year.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ I was feeling better.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>If you had no money, you</t>
+          <t>If you had no money, you (1) _________ buy food.</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>This is</t>
+          <t>This is (1) _________ I have tried paragliding.</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>about the appointment.</t>
+          <t>might have forgotten</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>that we left early.</t>
+          <t>such a crowded party</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>a new business last year.</t>
+          <t>set up</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>I was feeling better.</t>
+          <t>asked me if</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>buy food.</t>
+          <t>wouldn't be able to</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>I have tried paragliding.</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>wouldn't</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>the first</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>have forgotten</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>a crowded party</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>me if</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>be able to</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>time</t>
+          <t>the first time</t>
         </is>
       </c>
     </row>
@@ -1917,122 +1433,62 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Has the broken lift</t>
+          <t>Has the broken lift (1) _________ yet?</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>He isn't</t>
+          <t>He isn't (1) _________ to give a public speech.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ yesterday.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>He has</t>
+          <t>He has (1) _________ smoking.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>She is</t>
+          <t>She is (1) _________ candidate.</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>I haven't</t>
+          <t>I haven't (1) _________ last month.</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>yet?</t>
+          <t>been repaired</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>to give a public speech.</t>
+          <t>calm enough</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>yesterday.</t>
+          <t>had her hair cut</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>smoking.</t>
+          <t>given up</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>candidate.</t>
+          <t>the most experienced</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>last month.</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>calm</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>given</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>the most</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>spoken</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>repaired</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>her hair cut</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>experienced</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>to him since</t>
+          <t>spoken to him since</t>
         </is>
       </c>
     </row>
@@ -2104,122 +1560,62 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>You can use my laptop</t>
+          <t>You can use my laptop (1) _________ you are careful.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>The performance</t>
+          <t>The performance (1) _________ by thousands of people.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Her sister is</t>
+          <t>Her sister is (1) _________ her.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ for the tickets.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>He finished his homework</t>
+          <t>He finished his homework (1) _________ tired.</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ chess twenty years ago.</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>you are careful.</t>
+          <t>as long as</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>by thousands of people.</t>
+          <t>was seen</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>her.</t>
+          <t>taller than</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>for the tickets.</t>
+          <t>needn't pay</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>tired.</t>
+          <t>despite being</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>chess twenty years ago.</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>as long</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>taller</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>needn't</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>despite</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>started</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>seen</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>than</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>pay</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>playing</t>
+          <t>started playing</t>
         </is>
       </c>
     </row>
@@ -2291,122 +1687,62 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>I have</t>
+          <t>I have (1) _________ Tokyo before.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Pete's car is</t>
+          <t>Pete's car is (1) _________ Mark's.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ two coffees a day.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>If she hadn't helped me, I</t>
+          <t>If she hadn't helped me, I (1) _________ the exam.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>A new hospital is</t>
+          <t>A new hospital is (1) _________ at the moment.</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>The manager</t>
+          <t>The manager (1) _________ late again.</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Tokyo before.</t>
+          <t>never visited</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Mark's.</t>
+          <t>more expensive than</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>two coffees a day.</t>
+          <t>used to drink</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>the exam.</t>
+          <t>wouldn't have passed</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>at the moment.</t>
+          <t>being built</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>late again.</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>more expensive</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>wouldn't</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>told</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>visited</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>than</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>drink</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>have passed</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>built</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>him not to be</t>
+          <t>told him not to be</t>
         </is>
       </c>
     </row>
@@ -2478,122 +1814,62 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>I got</t>
+          <t>I got (1) _________ at the jeweller's.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that I couldn't eat it.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>She wasn't brave</t>
+          <t>She wasn't brave (1) _________ the new job.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ Canada in 2018.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Can you</t>
+          <t>Can you (1) _________ the dog this weekend?</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ visiting her aunt the next day.</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>at the jeweller's.</t>
+          <t>my watch repaired</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>that I couldn't eat it.</t>
+          <t>such hot soup</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>the new job.</t>
+          <t>enough to start</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Canada in 2018.</t>
+          <t>moved to</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>the dog this weekend?</t>
+          <t>look after</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>visiting her aunt the next day.</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>my watch</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>look</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>said</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>repaired</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>hot soup</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>to start</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>(that) she was</t>
+          <t>said (that) she was</t>
         </is>
       </c>
     </row>
@@ -2665,122 +1941,62 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>The car</t>
+          <t>The car (1) _________ last night.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>She can't</t>
+          <t>She can't (1) _________ the money.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that everyone passed.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>He has</t>
+          <t>He has (1) _________ eating meat.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Would you</t>
+          <t>Would you (1) _________ the window?</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Jane didn't do as</t>
+          <t>Jane didn't do as (1) _________ Tom on the test.</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>last night.</t>
+          <t>was broken into</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>the money.</t>
+          <t>have stolen</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>that everyone passed.</t>
+          <t>such an easy exam</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>eating meat.</t>
+          <t>given up</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>the window?</t>
+          <t>mind opening</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Tom on the test.</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>given</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>mind</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>well</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>broken into</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>stolen</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>an easy exam</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>opening</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>as</t>
+          <t>well as</t>
         </is>
       </c>
     </row>
@@ -2852,122 +2068,62 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>The winner will</t>
+          <t>The winner will (1) _________ at noon.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ like that.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>The ladder wasn't</t>
+          <t>The ladder wasn't (1) _________ to reach the roof.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>She finally</t>
+          <t>She finally (1) _________ a new flat.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>The doctor</t>
+          <t>The doctor (1) _________ eating fast food.</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>He has been working at this company</t>
+          <t>He has been working at this company (1) _________ years.</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>at noon.</t>
+          <t>be announced</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>like that.</t>
+          <t>shouldn't have spoken</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>to reach the roof.</t>
+          <t>long enough</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>a new flat.</t>
+          <t>managed to find</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>eating fast food.</t>
+          <t>told her to stop</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>years.</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>be</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>shouldn't</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>managed</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>told</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>announced</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>have spoken</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>to find</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>her to stop</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>five</t>
+          <t>for five</t>
         </is>
       </c>
     </row>
@@ -3039,122 +2195,62 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>The office</t>
+          <t>The office (1) _________ every day.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>I have</t>
+          <t>I have (1) _________ such an interesting book.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>He isn't</t>
+          <t>He isn't (1) _________ to say sorry.</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ jogging before breakfast.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>You'll get a discount</t>
+          <t>You'll get a discount (1) _________ a member.</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ had arrived.</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>every day.</t>
+          <t>is cleaned</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>such an interesting book.</t>
+          <t>never read</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>to say sorry.</t>
+          <t>humble enough</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>jogging before breakfast.</t>
+          <t>used to go</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>a member.</t>
+          <t>provided you're</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>had arrived.</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>humble</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>provided</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>cleaned</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>go</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>you're</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>him what time he</t>
+          <t>asked him what time he</t>
         </is>
       </c>
     </row>
@@ -3226,122 +2322,62 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ the guitar despite the noise.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that they closed it.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ the last ticket online.</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>I hadn't</t>
+          <t>I hadn't (1) _________ about the delay.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>They went for a walk</t>
+          <t>They went for a walk (1) _________ it was raining heavily.</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>My grandfather</t>
+          <t>My grandfather (1) _________ on Sundays.</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>the guitar despite the noise.</t>
+          <t>kept playing</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>that they closed it.</t>
+          <t>such a dangerous road</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>the last ticket online.</t>
+          <t>managed to book</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>about the delay.</t>
+          <t>been informed</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>it was raining heavily.</t>
+          <t>even though</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>on Sundays.</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>kept</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>managed</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>playing</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>a dangerous road</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>to book</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>informed</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>though</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>fish</t>
+          <t>used to fish</t>
         </is>
       </c>
     </row>
@@ -3413,122 +2449,62 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>All the questions have already</t>
+          <t>All the questions have already (1) _________ .</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ more when I was young.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>The tower is</t>
+          <t>The tower is (1) _________ in the city.</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ out late.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ to the new Italian restaurant.</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ where the director lived.</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>been answered</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>more when I was young.</t>
+          <t>wish I had travelled</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>in the city.</t>
+          <t>the tallest building</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>out late.</t>
+          <t>let his daughter stay</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>to the new Italian restaurant.</t>
+          <t>suggest going</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>where the director lived.</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>the tallest</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>let</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>suggest</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>answered</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>I had travelled</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>building</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>his daughter stay</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>going</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>him</t>
+          <t>asked him</t>
         </is>
       </c>
     </row>
@@ -3600,122 +2576,62 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>The bridge hasn't</t>
+          <t>The bridge hasn't (1) _________ yet.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>The box isn't</t>
+          <t>The box isn't (1) _________ for me to carry.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the document.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ at Christmas.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>The keys</t>
+          <t>The keys (1) _________ on the table.</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>The athlete</t>
+          <t>The athlete (1) _________ in the race.</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>yet.</t>
+          <t>been finished</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>for me to carry.</t>
+          <t>light enough</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>the document.</t>
+          <t>made me sign</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>at Christmas.</t>
+          <t>last visited his parents</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>on the table.</t>
+          <t>must be</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>in the race.</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>made</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>last</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>ran</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>finished</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>me sign</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>visited his parents</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>be</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>the fastest</t>
+          <t>ran the fastest</t>
         </is>
       </c>
     </row>
@@ -3787,122 +2703,62 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ collecting stamps since she was eight.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ your phone in class.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>The Volga is</t>
+          <t>The Volga is (1) _________ in Europe.</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ yoga last year.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ submit the form.</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>She stayed cheerful</t>
+          <t>She stayed cheerful (1) _________ she worked long hours.</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>collecting stamps since she was eight.</t>
+          <t>has been</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>your phone in class.</t>
+          <t>must not use</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>in Europe.</t>
+          <t>the longest river</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>yoga last year.</t>
+          <t>started doing</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>submit the form.</t>
+          <t>reminded me to</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>she worked long hours.</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>has</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>the longest</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>started</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>reminded</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>not use</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>river</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>doing</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>me to</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>though</t>
+          <t>even though</t>
         </is>
       </c>
     </row>
@@ -3974,122 +2830,62 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>All the candidates are</t>
+          <t>All the candidates are (1) _________ today.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>I've</t>
+          <t>I've (1) _________ a better pizza.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>There was</t>
+          <t>There was (1) _________ that I missed the meeting.</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the difficult puzzle in the end.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ carry the boxes.</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ the homework.</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>today.</t>
+          <t>being interviewed</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>a better pizza.</t>
+          <t>never eaten</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>that I missed the meeting.</t>
+          <t>such bad traffic</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>the difficult puzzle in the end.</t>
+          <t>managed to solve</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>carry the boxes.</t>
+          <t>asked him to help</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>the homework.</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>managed</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>interviewed</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>eaten</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>bad traffic</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>to solve</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>him to help</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>have done</t>
+          <t>must have done</t>
         </is>
       </c>
     </row>
@@ -4161,122 +2957,62 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>All the sandwiches had already</t>
+          <t>All the sandwiches had already (1) _________ .</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>We didn't leave</t>
+          <t>We didn't leave (1) _________ to catch the last train.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ on her phone during dinner.</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ up late.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>She gave a great presentation</t>
+          <t>She gave a great presentation (1) _________ nervous.</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>All the invitations will be</t>
+          <t>All the invitations will be (1) _________ tomorrow.</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>been eaten</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>to catch the last train.</t>
+          <t>early enough</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>on her phone during dinner.</t>
+          <t>kept talking</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>up late.</t>
+          <t>used to stay</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>nervous.</t>
+          <t>although she felt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>tomorrow.</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>early</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>kept</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>although</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>eaten</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>talking</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>stay</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>she felt</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>by the secretary</t>
+          <t>sent by the secretary</t>
         </is>
       </c>
     </row>
@@ -4348,122 +3084,62 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Breakfast (1) _________ from seven o'clock.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>I last spoke to my cousin</t>
+          <t>I last spoke to my cousin (1) _________ months.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>His brother is</t>
+          <t>His brother is (1) _________ him.</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>What (1) _________ a different route?</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>The manager</t>
+          <t>The manager (1) _________ due to snow.</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ him.</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>from seven o'clock.</t>
+          <t>is served</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>months.</t>
+          <t>six months ago</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>him.</t>
+          <t>a faster runner than</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>a different route?</t>
+          <t>about taking</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>due to snow.</t>
+          <t>called off all deliveries</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>him.</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>six</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>a faster</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>about</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>called</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>should</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>served</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>months ago</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>runner than</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>taking</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>off all deliveries</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>have invited</t>
+          <t>should have invited</t>
         </is>
       </c>
     </row>
@@ -4535,122 +3211,62 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ a printed copy.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that we watched it twice.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>We</t>
+          <t>We (1) _________ the museum was free on Sundays.</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ enough money when I was younger.</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>The window</t>
+          <t>The window (1) _________ before we arrived.</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Do you</t>
+          <t>Do you (1) _________ this jacket costs?</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>a printed copy.</t>
+          <t>needn't send</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>that we watched it twice.</t>
+          <t>such an informative documentary</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>the museum was free on Sundays.</t>
+          <t>found out that</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>enough money when I was younger.</t>
+          <t>wish I had saved</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>before we arrived.</t>
+          <t>had been broken</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>this jacket costs?</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>needn't</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>found</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>know</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>send</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>an informative documentary</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>out that</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>I had saved</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>been broken</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>how much</t>
+          <t>know how much</t>
         </is>
       </c>
     </row>
@@ -4722,122 +3338,62 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>All the dishes</t>
+          <t>All the dishes (1) _________ by a famous chef.</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>His colleague works</t>
+          <t>His colleague works (1) _________ him.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>She wasn't</t>
+          <t>She wasn't (1) _________ to go to the party.</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ their rooms.</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ to school.</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>They sat outside</t>
+          <t>They sat outside (1) _________ cold.</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>by a famous chef.</t>
+          <t>were cooked</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>him.</t>
+          <t>harder than</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>to go to the party.</t>
+          <t>awake enough</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>their rooms.</t>
+          <t>made the children tidy</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>to school.</t>
+          <t>used to take the bus</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>cold.</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>were</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>harder</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>awake</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>made</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>despite</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>cooked</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>than</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>the children tidy</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>take the bus</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>the</t>
+          <t>despite the</t>
         </is>
       </c>
     </row>
@@ -4909,122 +3465,62 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>The windows are</t>
+          <t>The windows are (1) _________ right now.</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>They can't</t>
+          <t>They can't (1) _________ the rules.</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ seen me for ages.</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the meeting until Friday.</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>I have</t>
+          <t>I have (1) _________ such a delicious meal.</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>He has been learning to drive</t>
+          <t>He has been learning to drive (1) _________ months.</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>right now.</t>
+          <t>being cleaned</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>the rules.</t>
+          <t>have broken</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>seen me for ages.</t>
+          <t>said (that) he hadn't</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>the meeting until Friday.</t>
+          <t>put off</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>such a delicious meal.</t>
+          <t>never tasted</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>months.</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>said</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>put</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>cleaned</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>broken</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>(that) he hadn't</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>off</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tasted</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>six</t>
+          <t>for six</t>
         </is>
       </c>
     </row>
@@ -5096,122 +3592,62 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ a doctor.</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>My flat is not</t>
+          <t>My flat is not (1) _________ John's.</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that we had a picnic.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the exam.</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ video games.</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>A fire</t>
+          <t>A fire (1) _________ broken out.</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>a doctor.</t>
+          <t>ought to see</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>John's.</t>
+          <t>as big as</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>that we had a picnic.</t>
+          <t>such beautiful weather</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>the exam.</t>
+          <t>had to retake</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>video games.</t>
+          <t>used to play</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>broken out.</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>ought</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>as big</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>was reported</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>to see</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>beautiful weather</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>to retake</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>play</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>to have</t>
+          <t>was reported to have</t>
         </is>
       </c>
     </row>
@@ -5283,122 +3719,62 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Many of the paintings have</t>
+          <t>Many of the paintings have (1) _________ by visitors.</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>It wasn't</t>
+          <t>It wasn't (1) _________ to go swimming.</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>She failed the test</t>
+          <t>She failed the test (1) _________ hard.</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ the cake.</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>I used to</t>
+          <t>I used to (1) _________ every day.</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>I have</t>
+          <t>I have (1) _________ such a large lake before.</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>by visitors.</t>
+          <t>been damaged</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>to go swimming.</t>
+          <t>warm enough</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>hard.</t>
+          <t>despite working</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>the cake.</t>
+          <t>admitted eating</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>every day.</t>
+          <t>be driven to school</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>such a large lake before.</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>warm</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>despite</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>be driven</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>damaged</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>working</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>eating</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>to school</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>seen</t>
+          <t>never seen</t>
         </is>
       </c>
     </row>
@@ -5470,122 +3846,62 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>A parcel is</t>
+          <t>A parcel is (1) _________ for you.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>She has</t>
+          <t>She has (1) _________ in a helicopter before.</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>His partner is</t>
+          <t>His partner is (1) _________ him.</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Their father</t>
+          <t>Their father (1) _________ a dog.</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>She started her own business</t>
+          <t>She started her own business (1) _________ there were risks.</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ to work.</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>for you.</t>
+          <t>being delivered</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>in a helicopter before.</t>
+          <t>never flown</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>him.</t>
+          <t>better organised than</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>a dog.</t>
+          <t>was persuaded to buy</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>there were risks.</t>
+          <t>even though</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>to work.</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>was persuaded</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>delivered</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>flown</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>organised than</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>to buy</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>though</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>cycle</t>
+          <t>used to cycle</t>
         </is>
       </c>
     </row>
@@ -5657,122 +3973,62 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>You don't</t>
+          <t>You don't (1) _________ in advance.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that I couldn't lift it.</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the driving test.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>He has</t>
+          <t>He has (1) _________ drinking coffee.</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>If he hadn't advised me, I</t>
+          <t>If he hadn't advised me, I (1) _________ the wrong choice.</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ that word meant.</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>in advance.</t>
+          <t>have to book</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>that I couldn't lift it.</t>
+          <t>such a heavy suitcase</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>the driving test.</t>
+          <t>managed to pass</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>drinking coffee.</t>
+          <t>given up</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>the wrong choice.</t>
+          <t>would have made</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>that word meant.</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>managed</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>given</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>would</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>to book</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>a heavy suitcase</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>to pass</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>have made</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>what</t>
+          <t>asked what</t>
         </is>
       </c>
     </row>
@@ -5844,122 +4100,62 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>The kitchen hasn't</t>
+          <t>The kitchen hasn't (1) _________ for days.</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>He was</t>
+          <t>He was (1) _________ lead the team.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>The robbery is</t>
+          <t>The robbery is (1) _________ by the police.</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ if I had enjoyed the concert.</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>He spoke clearly</t>
+          <t>He spoke clearly (1) _________ nervous.</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>I've</t>
+          <t>I've (1) _________ a better film this year.</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>for days.</t>
+          <t>been cleaned</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>lead the team.</t>
+          <t>too inexperienced to</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>by the police.</t>
+          <t>being investigated</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>if I had enjoyed the concert.</t>
+          <t>asked me</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>nervous.</t>
+          <t>even though he was</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>a better film this year.</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>too</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>cleaned</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>inexperienced to</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>investigated</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>me</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>though he was</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>seen</t>
+          <t>never seen</t>
         </is>
       </c>
     </row>
@@ -6031,122 +4227,62 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>The road outside is</t>
+          <t>The road outside is (1) _________ .</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the office already.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>There was</t>
+          <t>There was (1) _________ that people were standing.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>I last spoke to my old friend</t>
+          <t>I last spoke to my old friend (1) _________ years.</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>He was</t>
+          <t>He was (1) _________ the burning building.</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ from her job.</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>being repaired</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>the office already.</t>
+          <t>must have left</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>that people were standing.</t>
+          <t>such a full concert hall</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>years.</t>
+          <t>years ago</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>the burning building.</t>
+          <t>able to escape from</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>from her job.</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>able</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>repaired</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>have left</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>a full concert hall</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>ago</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>to escape from</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>to resign</t>
+          <t>had to resign</t>
         </is>
       </c>
     </row>
@@ -6218,122 +4354,62 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>The telephone</t>
+          <t>The telephone (1) _________ in the 1870s.</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>The result was</t>
+          <t>The result was (1) _________ that no one expected it.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>You can stay here</t>
+          <t>You can stay here (1) _________ well.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>She wasn't</t>
+          <t>She wasn't (1) _________ to ask for help.</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ call me the next day.</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>This would be</t>
+          <t>This would be (1) _________ I go on a cruise.</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>in the 1870s.</t>
+          <t>was invented</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>that no one expected it.</t>
+          <t>so surprising</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>well.</t>
+          <t>provided you behave</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>to ask for help.</t>
+          <t>confident enough</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>call me the next day.</t>
+          <t>said (that) he would</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>I go on a cruise.</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>so</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>provided</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>confident</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>said</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>the first</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>invented</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>surprising</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>you behave</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>(that) he would</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>time</t>
+          <t>the first time</t>
         </is>
       </c>
     </row>
@@ -6405,122 +4481,62 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Someone</t>
+          <t>Someone (1) _________ in the seventeenth century.</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>The festival wasn't</t>
+          <t>The festival wasn't (1) _________ to go to.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ not to trust him.</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ with his sister.</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>They bought the house</t>
+          <t>They bought the house (1) _________ it was very expensive.</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>She has been studying for her degree</t>
+          <t>She has been studying for her degree (1) _________ years.</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>in the seventeenth century.</t>
+          <t>painted this</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>to go to.</t>
+          <t>close enough</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>not to trust him.</t>
+          <t>warned me</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>with his sister.</t>
+          <t>used to argue</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>it was very expensive.</t>
+          <t>even though</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>years.</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>painted</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>close</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>warned</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>this</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>me</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>argue</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>though</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>three</t>
+          <t>for three</t>
         </is>
       </c>
     </row>
@@ -6592,122 +4608,62 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ a tie.</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>I have</t>
+          <t>I have (1) _________ such an exciting match.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lisa is</t>
+          <t>Lisa is (1) _________ Tom.</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ so much money on the car.</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>My boss</t>
+          <t>My boss (1) _________ home.</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>She fell asleep quickly</t>
+          <t>She fell asleep quickly (1) _________ there was a lot of noise.</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>a tie.</t>
+          <t>needn't wear</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>such an exciting match.</t>
+          <t>never watched</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Tom.</t>
+          <t>more creative than</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>so much money on the car.</t>
+          <t>wishes he hadn't spent</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>home.</t>
+          <t>let me work from</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>there was a lot of noise.</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>needn't</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>more creative</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>wishes</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>let</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>wear</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>watched</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>than</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>he hadn't spent</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>me work from</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>though</t>
+          <t>even though</t>
         </is>
       </c>
     </row>
@@ -6779,122 +4735,62 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>The project</t>
+          <t>The project (1) _________ ahead of schedule.</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the truth.</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that schools were closed.</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ before bedtime.</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ .</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>The coach</t>
+          <t>The coach (1) _________ harder.</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>ahead of schedule.</t>
+          <t>was completed</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>the truth.</t>
+          <t>must be telling</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>that schools were closed.</t>
+          <t>such a severe storm</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>before bedtime.</t>
+          <t>used to read</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>should have apologised</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>harder.</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>should</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>told</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>be telling</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>a severe storm</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>have apologised</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>the players to train</t>
+          <t>told the players to train</t>
         </is>
       </c>
     </row>
@@ -6966,122 +4862,62 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>She has been living abroad</t>
+          <t>She has been living abroad (1) _________ years.</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>He is</t>
+          <t>He is (1) _________ his colleague.</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ even after midnight.</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>They were</t>
+          <t>They were (1) _________ tickets.</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ if he had ever visited Australia.</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ golf after he retired.</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>years.</t>
+          <t>for five</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>his colleague.</t>
+          <t>less skilful than</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>even after midnight.</t>
+          <t>kept studying</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>tickets.</t>
+          <t>unable to get</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>if he had ever visited Australia.</t>
+          <t>asked him</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>golf after he retired.</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>less skilful</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>kept</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>unable</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>started</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>five</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>than</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>studying</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>to get</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>him</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>playing</t>
+          <t>started playing</t>
         </is>
       </c>
     </row>
@@ -7153,122 +4989,62 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>The office had</t>
+          <t>The office had (1) _________ before we arrived.</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that she took a month to read it.</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ working overtime.</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Tom is</t>
+          <t>Tom is (1) _________ in his class.</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>He didn't improve</t>
+          <t>He didn't improve (1) _________ every day.</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>The manager</t>
+          <t>The manager (1) _________ on time.</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>before we arrived.</t>
+          <t>been tidied</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>that she took a month to read it.</t>
+          <t>such a long book</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>working overtime.</t>
+          <t>gave up</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>in his class.</t>
+          <t>the tallest boy</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>every day.</t>
+          <t>despite practising</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>on time.</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>gave</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>the tallest</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>despite</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>told</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>tidied</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>a long book</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>boy</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>practising</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>them to arrive</t>
+          <t>told them to arrive</t>
         </is>
       </c>
     </row>
@@ -7340,122 +5116,62 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>The city centre is</t>
+          <t>The city centre is (1) _________ .</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>I have</t>
+          <t>I have (1) _________ a celebrity before.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>The stairs aren't</t>
+          <t>The stairs aren't (1) _________ for elderly people.</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ at dawn.</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ where he had grown up.</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>If we hadn't had the map, we</t>
+          <t>If we hadn't had the map, we (1) _________ lost.</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>being expanded</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>a celebrity before.</t>
+          <t>never met</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>for elderly people.</t>
+          <t>gentle enough</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>at dawn.</t>
+          <t>used to exercise</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>where he had grown up.</t>
+          <t>asked him</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>lost.</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>gentle</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>would</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>expanded</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>met</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>exercise</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>him</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>have got</t>
+          <t>would have got</t>
         </is>
       </c>
     </row>
@@ -7527,122 +5243,62 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>The roof had</t>
+          <t>The roof had (1) _________ by the time it started raining.</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>He is not</t>
+          <t>He is not (1) _________ he used to be.</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>The task wasn't</t>
+          <t>The task wasn't (1) _________ for him to complete alone.</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ to bed at nine.</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>The match continued</t>
+          <t>The match continued (1) _________ the weather was bad.</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>She probably didn't hear you</t>
+          <t>She probably didn't hear you (1) _________ the loud music.</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>by the time it started raining.</t>
+          <t>been repaired</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>he used to be.</t>
+          <t>more organised than</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>for him to complete alone.</t>
+          <t>simple enough</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>to bed at nine.</t>
+          <t>made the children go</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>the weather was bad.</t>
+          <t>even though</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>the loud music.</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>more organised</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>simple</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>made</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>because</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>repaired</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>than</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>the children go</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>though</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>of</t>
+          <t>because of</t>
         </is>
       </c>
     </row>
@@ -7714,122 +5370,62 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>You don't</t>
+          <t>You don't (1) _________ late.</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>They were</t>
+          <t>They were (1) _________ that the class had to retake it.</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ a promotion.</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ the news at ten.</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ already sent the email.</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>It is</t>
+          <t>It is (1) _________ without saying goodbye.</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>late.</t>
+          <t>have to stay</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>that the class had to retake it.</t>
+          <t>such poor results</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>a promotion.</t>
+          <t>managed to get</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>the news at ten.</t>
+          <t>used to watch</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>already sent the email.</t>
+          <t>said (that) she had</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>without saying goodbye.</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>managed</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>said</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>possible</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>to stay</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>poor results</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>to get</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>watch</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>(that) she had</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>that he left</t>
+          <t>possible that he left</t>
         </is>
       </c>
     </row>
@@ -7901,122 +5497,62 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>All the broken benches are</t>
+          <t>All the broken benches are (1) _________ .</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ his passport.</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>I have</t>
+          <t>I have (1) _________ such a peaceful place.</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ free on Saturday.</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ after her operation.</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>If she hadn't encouraged me, I</t>
+          <t>If she hadn't encouraged me, I (1) _________ .</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>being repaired</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>his passport.</t>
+          <t>must have forgotten</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>such a peaceful place.</t>
+          <t>never been to</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>free on Saturday.</t>
+          <t>asked me if I was</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>after her operation.</t>
+          <t>started swimming</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>started</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>would</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>repaired</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>have forgotten</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>been to</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>me if I was</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>swimming</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>have quit</t>
+          <t>would have quit</t>
         </is>
       </c>
     </row>
@@ -8088,122 +5624,62 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>The back door had</t>
+          <t>The back door had (1) _________ unlocked.</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>She is</t>
+          <t>She is (1) _________ she looks.</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>He wasn't</t>
+          <t>He wasn't (1) _________ to enter the dark room.</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the opportunity.</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ the market on Saturdays.</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ tell anyone.</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>unlocked.</t>
+          <t>been left</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>she looks.</t>
+          <t>less confident than</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>to enter the dark room.</t>
+          <t>brave enough</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>the opportunity.</t>
+          <t>wishes she had taken</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>the market on Saturdays.</t>
+          <t>used to go to</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>tell anyone.</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>less confident</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>brave</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>wishes</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>than</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>she had taken</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>go to</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>him not to</t>
+          <t>asked him not to</t>
         </is>
       </c>
     </row>
@@ -8275,122 +5751,62 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>This cheese</t>
+          <t>This cheese (1) _________ only in one village.</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that we could barely move.</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>She has been working at the company</t>
+          <t>She has been working at the company (1) _________ years.</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ a specialist about your knee.</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>We enjoyed the film</t>
+          <t>We enjoyed the film (1) _________ long.</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>She asked</t>
+          <t>She asked (1) _________ started.</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>only in one village.</t>
+          <t>is produced</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>that we could barely move.</t>
+          <t>such a small room</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>years.</t>
+          <t>for four</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>a specialist about your knee.</t>
+          <t>ought to see</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>long.</t>
+          <t>despite it being</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>started.</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>ought</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>despite</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>what</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>produced</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>a small room</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>four</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>to see</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>it being</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>time the concert</t>
+          <t>what time the concert</t>
         </is>
       </c>
     </row>
@@ -8462,122 +5878,62 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ in advance.</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>He is</t>
+          <t>He is (1) _________ he used to be.</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ even though she was exhausted.</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ a fine for parking illegally.</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ to my party.</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>If they hadn't had the map, they would</t>
+          <t>If they hadn't had the map, they would (1) _________ lost.</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>in advance.</t>
+          <t>don't need to register</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>he used to be.</t>
+          <t>lazier than</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>even though she was exhausted.</t>
+          <t>kept running</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>a fine for parking illegally.</t>
+          <t>had to pay</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>to my party.</t>
+          <t>promised to come</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>lost.</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>don't</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>lazier</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>kept</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>promised</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>need to register</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr">
-        <is>
-          <t>than</t>
-        </is>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>to pay</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>to come</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>got</t>
+          <t>have got</t>
         </is>
       </c>
     </row>
@@ -8649,122 +6005,62 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>All the chairs have</t>
+          <t>All the chairs have (1) _________ from the room.</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ the answer.</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that we took lots of photos.</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ he had ever worked abroad.</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>She loved her job</t>
+          <t>She loved her job (1) _________ she was poorly paid.</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ rock climbing at the age of forty.</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>from the room.</t>
+          <t>been taken</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>the answer.</t>
+          <t>must know</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>that we took lots of photos.</t>
+          <t>such a spectacular view</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>he had ever worked abroad.</t>
+          <t>asked him if</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>she was poorly paid.</t>
+          <t>even though</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>rock climbing at the age of forty.</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>started</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>taken</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>know</t>
-        </is>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>a spectacular view</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>him if</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>though</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>doing</t>
+          <t>started doing</t>
         </is>
       </c>
     </row>
@@ -8836,118 +6132,62 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>The town hall is</t>
+          <t>The town hall is (1) _________ this year.</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>This is</t>
+          <t>This is (1) _________ restaurant in the neighbourhood.</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>She wasn't</t>
+          <t>She wasn't (1) _________ to reply to all the messages.</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ in touch with his old friends.</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ a shopping list.</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>The teacher</t>
+          <t>The teacher (1) _________ in their essays that day.</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>this year.</t>
+          <t>being renovated</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>restaurant in the neighbourhood.</t>
+          <t>the cheapest</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>to reply to all the messages.</t>
+          <t>free enough</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>in touch with his old friends.</t>
+          <t>wishes he had kept</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>a shopping list.</t>
+          <t>used to make</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>in their essays that day.</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>the cheapest</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>wishes</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>told</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>renovated</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>he had kept</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>make</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>the class to hand</t>
+          <t>told the class to hand</t>
         </is>
       </c>
     </row>
@@ -9019,122 +6259,62 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>The extension</t>
+          <t>The extension (1) _________ in just six weeks.</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the flight.</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>I've</t>
+          <t>I've (1) _________ such a funny programme.</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the door.</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Most students passed</t>
+          <t>Most students passed (1) _________ hard.</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>He has been collecting rare coins</t>
+          <t>He has been collecting rare coins (1) _________ ten.</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>in just six weeks.</t>
+          <t>was built</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>the flight.</t>
+          <t>might have missed</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>such a funny programme.</t>
+          <t>never seen</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>the door.</t>
+          <t>asked me to open</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>hard.</t>
+          <t>despite the exam being</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>ten.</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>despite</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>since</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>built</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>have missed</t>
-        </is>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>seen</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>me to open</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>the exam being</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>he was</t>
+          <t>since he was</t>
         </is>
       </c>
     </row>
@@ -9206,122 +6386,62 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>He doesn't</t>
+          <t>He doesn't (1) _________ every meeting.</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that we missed our flight.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>She eventually</t>
+          <t>She eventually (1) _________ the problem.</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>He kept trying</t>
+          <t>He kept trying (1) _________ there were setbacks.</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>She hasn't been abroad</t>
+          <t>She hasn't been abroad (1) _________ years.</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ her job.</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>every meeting.</t>
+          <t>have to attend</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>that we missed our flight.</t>
+          <t>such a long traffic jam</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>the problem.</t>
+          <t>managed to solve</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>there were setbacks.</t>
+          <t>even though</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>years.</t>
+          <t>for three</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>her job.</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>managed</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>talked</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>to attend</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr">
-        <is>
-          <t>a long traffic jam</t>
-        </is>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>to solve</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>though</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>three</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>her out of quitting</t>
+          <t>talked her out of quitting</t>
         </is>
       </c>
     </row>
@@ -9393,122 +6513,62 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ inside the gallery.</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>She is</t>
+          <t>She is (1) _________ writer in the country.</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>She wasn't</t>
+          <t>She wasn't (1) _________ to speak in public.</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ the window.</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ a diary.</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>She asked him</t>
+          <t>She asked him (1) _________ closed.</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>inside the gallery.</t>
+          <t>must not take photos</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>writer in the country.</t>
+          <t>the most popular</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>to speak in public.</t>
+          <t>relaxed enough</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>the window.</t>
+          <t>admitted breaking</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>a diary.</t>
+          <t>used to keep</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>closed.</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>the most</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>relaxed</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>when</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>not take photos</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>popular</t>
-        </is>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>breaking</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>the exhibition</t>
+          <t>when the exhibition</t>
         </is>
       </c>
     </row>
@@ -9580,122 +6640,62 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>A new policy had</t>
+          <t>A new policy had (1) _________ the previous year.</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>He isn't</t>
+          <t>He isn't (1) _________ to ride the biggest roller coaster.</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the job offer.</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ that house when I had the chance.</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ his holiday due to work.</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>The journalist</t>
+          <t>The journalist (1) _________ the decision.</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>the previous year.</t>
+          <t>been introduced</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>to ride the biggest roller coaster.</t>
+          <t>tall enough</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>the job offer.</t>
+          <t>told nobody about</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>that house when I had the chance.</t>
+          <t>wish I had bought</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>his holiday due to work.</t>
+          <t>had to cancel</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>the decision.</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>told</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>asked</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>introduced</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>enough</t>
-        </is>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>nobody about</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>I had bought</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>to cancel</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>the mayor to explain</t>
+          <t>asked the mayor to explain</t>
         </is>
       </c>
     </row>
@@ -9767,122 +6767,62 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>A new library is</t>
+          <t>A new library is (1) _________ near the park.</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>He can't</t>
+          <t>He can't (1) _________ in the exam.</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that she recommended it.</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>She asked him</t>
+          <t>She asked him (1) _________ cook pasta.</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>He was</t>
+          <t>He was (1) _________ making all the decisions.</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>She won the match</t>
+          <t>She won the match (1) _________ the first set.</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>near the park.</t>
+          <t>being built</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>in the exam.</t>
+          <t>have cheated</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>that she recommended it.</t>
+          <t>such a useful course</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>cook pasta.</t>
+          <t>if he knew how to</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>making all the decisions.</t>
+          <t>responsible for</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>the first set.</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>if</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>responsible</t>
-        </is>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>built</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>cheated</t>
-        </is>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>a useful course</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>he knew how to</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>though she lost</t>
+          <t>even though she lost</t>
         </is>
       </c>
     </row>
@@ -9954,122 +6894,62 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>All the tables have already</t>
+          <t>All the tables have already (1) _________ .</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>She can't</t>
+          <t>She can't (1) _________ that mistake.</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that many people cried.</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ television in the evenings.</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>She bought the dress</t>
+          <t>She bought the dress (1) _________ high.</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ planning a surprise party.</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>been booked</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>that mistake.</t>
+          <t>have made</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>that many people cried.</t>
+          <t>such a moving documentary</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>television in the evenings.</t>
+          <t>used to watch</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>high.</t>
+          <t>despite the price being</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>planning a surprise party.</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>used to</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>despite</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>said</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>booked</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>made</t>
-        </is>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>a moving documentary</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>watch</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>the price being</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>(that) she was</t>
+          <t>said (that) she was</t>
         </is>
       </c>
     </row>
